--- a/datasets/output/6798_1000__Dataset4_FirstWithOutl__all_results__20260519_061338.xlsx
+++ b/datasets/output/6798_1000__Dataset4_FirstWithOutl__all_results__20260519_061338.xlsx
@@ -499,22 +499,22 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>134.8526815428244</v>
+        <v>132.3876561876193</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1288181359107458</v>
+        <v>0.1501707823121403</v>
       </c>
       <c r="H2" t="n">
-        <v>61.39725428684365</v>
+        <v>57.3390506328996</v>
       </c>
       <c r="I2" t="n">
-        <v>14.09918452396188</v>
+        <v>13.16722337274179</v>
       </c>
       <c r="J2" t="n">
-        <v>72.85469999999999</v>
+        <v>71.13079999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -536,22 +536,22 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>133.356646251274</v>
+        <v>131.0762367549251</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1273890469574571</v>
+        <v>0.1486832049365886</v>
       </c>
       <c r="H3" t="n">
-        <v>60.52895818646094</v>
+        <v>56.87261026269338</v>
       </c>
       <c r="I3" t="n">
-        <v>13.3754811695189</v>
+        <v>12.69563872474467</v>
       </c>
       <c r="J3" t="n">
-        <v>72.85469999999999</v>
+        <v>71.13079999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -573,22 +573,22 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>136.100581003548</v>
+        <v>130.3564482590442</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1300101929057964</v>
+        <v>0.147866730012578</v>
       </c>
       <c r="H4" t="n">
-        <v>62.37598050383799</v>
+        <v>58.11167000446395</v>
       </c>
       <c r="I4" t="n">
-        <v>14.49799512488929</v>
+        <v>13.61497169455465</v>
       </c>
       <c r="J4" t="n">
-        <v>72.85469999999999</v>
+        <v>71.13079999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -610,22 +610,22 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>135.2052333308443</v>
+        <v>134.7897485946206</v>
       </c>
       <c r="G5" t="n">
-        <v>0.129154911298711</v>
+        <v>0.1528955385797052</v>
       </c>
       <c r="H5" t="n">
-        <v>60.96896709785754</v>
+        <v>58.29708179132079</v>
       </c>
       <c r="I5" t="n">
-        <v>12.80537741396508</v>
+        <v>12.52632080455671</v>
       </c>
       <c r="J5" t="n">
-        <v>72.85469999999999</v>
+        <v>71.13079999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -647,22 +647,22 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>144.7785862223542</v>
+        <v>143.0127939015085</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1382998645898952</v>
+        <v>0.1622231540257668</v>
       </c>
       <c r="H6" t="n">
-        <v>64.76499657674114</v>
+        <v>62.67076650970473</v>
       </c>
       <c r="I6" t="n">
-        <v>13.00622441083402</v>
+        <v>12.98592546141079</v>
       </c>
       <c r="J6" t="n">
-        <v>72.85469999999999</v>
+        <v>71.13079999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -684,22 +684,22 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>144.4506164910147</v>
+        <v>134.3048648400382</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1379865712319659</v>
+        <v>0.1523455222499887</v>
       </c>
       <c r="H7" t="n">
-        <v>68.00366186844377</v>
+        <v>62.31918589956909</v>
       </c>
       <c r="I7" t="n">
-        <v>16.50122754906642</v>
+        <v>15.20662127749475</v>
       </c>
       <c r="J7" t="n">
-        <v>72.85469999999999</v>
+        <v>71.13079999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -721,22 +721,22 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>135.9030386244256</v>
+        <v>119.2636567070755</v>
       </c>
       <c r="G8" t="n">
-        <v>0.134895230700569</v>
+        <v>0.1395781338908679</v>
       </c>
       <c r="H8" t="n">
-        <v>60.51445824585028</v>
+        <v>56.44256737313805</v>
       </c>
       <c r="I8" t="n">
-        <v>13.74192139299837</v>
+        <v>13.91049962680813</v>
       </c>
       <c r="J8" t="n">
-        <v>86.8403</v>
+        <v>88.2903</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -758,22 +758,22 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>135.6693694187947</v>
+        <v>118.1169330075197</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1346632943014992</v>
+        <v>0.1382360858731256</v>
       </c>
       <c r="H9" t="n">
-        <v>60.33555105355357</v>
+        <v>55.65163094551747</v>
       </c>
       <c r="I9" t="n">
-        <v>13.24742553373889</v>
+        <v>13.41565209496972</v>
       </c>
       <c r="J9" t="n">
-        <v>86.8403</v>
+        <v>88.2903</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -795,22 +795,22 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>138.4247340770045</v>
+        <v>118.3110503886684</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1373982261690682</v>
+        <v>0.1384632677537136</v>
       </c>
       <c r="H10" t="n">
-        <v>62.68448335560573</v>
+        <v>57.35244234622265</v>
       </c>
       <c r="I10" t="n">
-        <v>14.40714028204843</v>
+        <v>14.43800182719928</v>
       </c>
       <c r="J10" t="n">
-        <v>86.8403</v>
+        <v>88.2903</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -832,22 +832,22 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>136.2533572563672</v>
+        <v>121.7648547149099</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1352429514958712</v>
+        <v>0.1425053672162936</v>
       </c>
       <c r="H11" t="n">
-        <v>60.34808584726373</v>
+        <v>56.67234268161713</v>
       </c>
       <c r="I11" t="n">
-        <v>12.78492295082829</v>
+        <v>12.93771331692706</v>
       </c>
       <c r="J11" t="n">
-        <v>86.8403</v>
+        <v>88.2903</v>
       </c>
       <c r="K11" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -869,22 +869,22 @@
         <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>141.3987055104648</v>
+        <v>130.8057107062179</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1403501437028784</v>
+        <v>0.1530861748393755</v>
       </c>
       <c r="H12" t="n">
-        <v>63.02669729534809</v>
+        <v>60.58010205666351</v>
       </c>
       <c r="I12" t="n">
-        <v>12.94565784092604</v>
+        <v>13.13984989750542</v>
       </c>
       <c r="J12" t="n">
-        <v>86.8403</v>
+        <v>88.2903</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -906,22 +906,22 @@
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>146.436638612426</v>
+        <v>123.1346438381052</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1453507173097804</v>
+        <v>0.144108475949654</v>
       </c>
       <c r="H13" t="n">
-        <v>68.1435189023142</v>
+        <v>62.04295882582504</v>
       </c>
       <c r="I13" t="n">
-        <v>16.26692862190073</v>
+        <v>16.19648020905283</v>
       </c>
       <c r="J13" t="n">
-        <v>86.8403</v>
+        <v>88.2903</v>
       </c>
       <c r="K13" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -943,22 +943,22 @@
         <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>129.6189747481323</v>
+        <v>131.3330939552707</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1313983845304127</v>
+        <v>0.1385312833473911</v>
       </c>
       <c r="H14" t="n">
-        <v>58.75992942122353</v>
+        <v>58.528638345198</v>
       </c>
       <c r="I14" t="n">
-        <v>13.60457180904642</v>
+        <v>13.62725763147841</v>
       </c>
       <c r="J14" t="n">
-        <v>90.0287</v>
+        <v>91.1484</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -980,22 +980,22 @@
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>128.2147530934158</v>
+        <v>132.2087408706736</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1299748857154366</v>
+        <v>0.1394549232868512</v>
       </c>
       <c r="H15" t="n">
-        <v>58.30601831034451</v>
+        <v>58.37363360798238</v>
       </c>
       <c r="I15" t="n">
-        <v>13.25466458717171</v>
+        <v>13.30745022585643</v>
       </c>
       <c r="J15" t="n">
-        <v>90.0287</v>
+        <v>91.1484</v>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -1017,22 +1017,22 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>129.3617581503358</v>
+        <v>134.2084064756541</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1311376368621754</v>
+        <v>0.1415641878612312</v>
       </c>
       <c r="H16" t="n">
-        <v>59.99453090312101</v>
+        <v>60.18697375121224</v>
       </c>
       <c r="I16" t="n">
-        <v>14.26750586219029</v>
+        <v>14.28029662024239</v>
       </c>
       <c r="J16" t="n">
-        <v>90.0287</v>
+        <v>91.1484</v>
       </c>
       <c r="K16" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1054,22 +1054,22 @@
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>129.7125656687449</v>
+        <v>134.7752691116972</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1314932602675422</v>
+        <v>0.1421621194722803</v>
       </c>
       <c r="H17" t="n">
-        <v>58.21956789602541</v>
+        <v>58.88741641806055</v>
       </c>
       <c r="I17" t="n">
-        <v>12.70503050342379</v>
+        <v>12.82551496358862</v>
       </c>
       <c r="J17" t="n">
-        <v>90.0287</v>
+        <v>91.1484</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -1091,22 +1091,22 @@
         <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>136.3928482200691</v>
+        <v>141.4195399052105</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1382652497633421</v>
+        <v>0.149170553768715</v>
       </c>
       <c r="H18" t="n">
-        <v>61.57703612287337</v>
+        <v>62.01685516117365</v>
       </c>
       <c r="I18" t="n">
-        <v>12.8110902612898</v>
+        <v>12.87147092032781</v>
       </c>
       <c r="J18" t="n">
-        <v>90.0287</v>
+        <v>91.1484</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -1128,22 +1128,22 @@
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>140.4119345721354</v>
+        <v>139.8813576313451</v>
       </c>
       <c r="G19" t="n">
-        <v>0.142339510148258</v>
+        <v>0.1475480658031657</v>
       </c>
       <c r="H19" t="n">
-        <v>65.9110804897181</v>
+        <v>64.63314748634564</v>
       </c>
       <c r="I19" t="n">
-        <v>16.03739936538247</v>
+        <v>16.10417900731462</v>
       </c>
       <c r="J19" t="n">
-        <v>90.0287</v>
+        <v>91.1484</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -1165,22 +1165,22 @@
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>125.8724038623935</v>
+        <v>131.7064417762021</v>
       </c>
       <c r="G20" t="n">
-        <v>0.131786350128996</v>
+        <v>0.1451256840160323</v>
       </c>
       <c r="H20" t="n">
-        <v>58.1118660438595</v>
+        <v>59.29176777776043</v>
       </c>
       <c r="I20" t="n">
-        <v>13.86486752507177</v>
+        <v>14.15741688664652</v>
       </c>
       <c r="J20" t="n">
-        <v>90.6688</v>
+        <v>91.84350000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -1202,22 +1202,22 @@
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>125.6379961501623</v>
+        <v>133.4308630896733</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1315409290844372</v>
+        <v>0.1470258023342735</v>
       </c>
       <c r="H21" t="n">
-        <v>58.34341891647939</v>
+        <v>59.49611211964304</v>
       </c>
       <c r="I21" t="n">
-        <v>13.64947655369214</v>
+        <v>13.89175821028286</v>
       </c>
       <c r="J21" t="n">
-        <v>90.6688</v>
+        <v>91.84350000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -1239,22 +1239,22 @@
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>127.8053628432603</v>
+        <v>132.417627233945</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1338101265980303</v>
+        <v>0.1459093303937286</v>
       </c>
       <c r="H22" t="n">
-        <v>59.99559242421801</v>
+        <v>60.78261139322646</v>
       </c>
       <c r="I22" t="n">
-        <v>14.59420096082989</v>
+        <v>14.77276955595709</v>
       </c>
       <c r="J22" t="n">
-        <v>90.6688</v>
+        <v>91.84350000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -1276,22 +1276,22 @@
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>125.5179543431495</v>
+        <v>134.5130868818701</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1314152472739396</v>
+        <v>0.1482182912207919</v>
       </c>
       <c r="H23" t="n">
-        <v>58.20428884708961</v>
+        <v>59.54138358555766</v>
       </c>
       <c r="I23" t="n">
-        <v>13.0883617365438</v>
+        <v>13.25613690896042</v>
       </c>
       <c r="J23" t="n">
-        <v>90.6688</v>
+        <v>91.84350000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -1313,22 +1313,22 @@
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>129.9120983934949</v>
+        <v>138.8350943457054</v>
       </c>
       <c r="G24" t="n">
-        <v>0.136015844295739</v>
+        <v>0.1529806572907621</v>
       </c>
       <c r="H24" t="n">
-        <v>60.5099427393958</v>
+        <v>62.18649109819818</v>
       </c>
       <c r="I24" t="n">
-        <v>12.98368654559749</v>
+        <v>13.22168051548931</v>
       </c>
       <c r="J24" t="n">
-        <v>90.6688</v>
+        <v>91.84350000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -1350,22 +1350,22 @@
         <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>134.3561040099501</v>
+        <v>137.7264461008112</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1406686455625334</v>
+        <v>0.1517590516296902</v>
       </c>
       <c r="H25" t="n">
-        <v>64.47040525100644</v>
+        <v>64.98146240795822</v>
       </c>
       <c r="I25" t="n">
-        <v>16.24660478901814</v>
+        <v>16.60572662300751</v>
       </c>
       <c r="J25" t="n">
-        <v>90.6688</v>
+        <v>91.84350000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -1387,22 +1387,22 @@
         <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>137.9954905893927</v>
+        <v>137.7638015467583</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1452782239776257</v>
+        <v>0.146275829845004</v>
       </c>
       <c r="H26" t="n">
-        <v>61.54706785258291</v>
+        <v>62.09824534746544</v>
       </c>
       <c r="I26" t="n">
-        <v>14.41157015449998</v>
+        <v>14.75092533323303</v>
       </c>
       <c r="J26" t="n">
-        <v>90.69410000000001</v>
+        <v>92.3171</v>
       </c>
       <c r="K26" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
@@ -1424,22 +1424,22 @@
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>137.091602215674</v>
+        <v>139.0587003984026</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1443266327549921</v>
+        <v>0.1476507367651308</v>
       </c>
       <c r="H27" t="n">
-        <v>62.39297000994593</v>
+        <v>62.87606140318784</v>
       </c>
       <c r="I27" t="n">
-        <v>14.5998413462532</v>
+        <v>14.83101411513438</v>
       </c>
       <c r="J27" t="n">
-        <v>90.69410000000001</v>
+        <v>92.3171</v>
       </c>
       <c r="K27" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1461,22 +1461,22 @@
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>138.1829600470848</v>
+        <v>138.2302822410116</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1454755871649822</v>
+        <v>0.1467711330370796</v>
       </c>
       <c r="H28" t="n">
-        <v>63.30305447906645</v>
+        <v>63.64932464055804</v>
       </c>
       <c r="I28" t="n">
-        <v>15.27505113796527</v>
+        <v>15.5102467026408</v>
       </c>
       <c r="J28" t="n">
-        <v>90.69410000000001</v>
+        <v>92.3171</v>
       </c>
       <c r="K28" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -1498,22 +1498,22 @@
         <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>136.597338480345</v>
+        <v>139.1406893193277</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1438062841744808</v>
+        <v>0.1477377915452093</v>
       </c>
       <c r="H29" t="n">
-        <v>61.90656767683568</v>
+        <v>62.21965657813723</v>
       </c>
       <c r="I29" t="n">
-        <v>13.95540210263719</v>
+        <v>14.02522551822888</v>
       </c>
       <c r="J29" t="n">
-        <v>90.69410000000001</v>
+        <v>92.3171</v>
       </c>
       <c r="K29" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1535,22 +1535,22 @@
         <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>138.9699309288406</v>
+        <v>143.8687089002901</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1463040905569067</v>
+        <v>0.1527579418311606</v>
       </c>
       <c r="H30" t="n">
-        <v>63.16048521497659</v>
+        <v>64.03146653276693</v>
       </c>
       <c r="I30" t="n">
-        <v>13.55415619390963</v>
+        <v>13.737423823822</v>
       </c>
       <c r="J30" t="n">
-        <v>90.69410000000001</v>
+        <v>92.3171</v>
       </c>
       <c r="K30" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
@@ -1572,22 +1572,22 @@
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>144.8104796211807</v>
+        <v>141.1625655303579</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1524528751110538</v>
+        <v>0.1498845936607994</v>
       </c>
       <c r="H31" t="n">
-        <v>66.4069741019273</v>
+        <v>66.98632316865127</v>
       </c>
       <c r="I31" t="n">
-        <v>16.61724354622425</v>
+        <v>16.95450374601157</v>
       </c>
       <c r="J31" t="n">
-        <v>90.69410000000001</v>
+        <v>92.3171</v>
       </c>
       <c r="K31" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -1609,22 +1609,22 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>138.8850935308035</v>
+        <v>133.3736739547289</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1494758478274263</v>
+        <v>0.142692520514777</v>
       </c>
       <c r="H32" t="n">
-        <v>62.81079840297274</v>
+        <v>62.51780699408337</v>
       </c>
       <c r="I32" t="n">
-        <v>14.9489902653113</v>
+        <v>15.20434362455762</v>
       </c>
       <c r="J32" t="n">
-        <v>90.44840000000001</v>
+        <v>91.38030000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1646,22 +1646,22 @@
         <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>140.9635987265546</v>
+        <v>135.2196388033666</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1517128505067649</v>
+        <v>0.1446674633143822</v>
       </c>
       <c r="H33" t="n">
-        <v>64.40252907675806</v>
+        <v>63.61382647737735</v>
       </c>
       <c r="I33" t="n">
-        <v>15.372468530587</v>
+        <v>15.62457052548026</v>
       </c>
       <c r="J33" t="n">
-        <v>90.44840000000001</v>
+        <v>91.38030000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -1683,22 +1683,22 @@
         <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>141.8233788740555</v>
+        <v>134.1440762108739</v>
       </c>
       <c r="G34" t="n">
-        <v>0.152638193631975</v>
+        <v>0.1435167509380681</v>
       </c>
       <c r="H34" t="n">
-        <v>64.90685403154546</v>
+        <v>64.1908448449239</v>
       </c>
       <c r="I34" t="n">
-        <v>15.82557378189575</v>
+        <v>16.10442429993149</v>
       </c>
       <c r="J34" t="n">
-        <v>90.44840000000001</v>
+        <v>91.38030000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1720,22 +1720,22 @@
         <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>141.2962661331711</v>
+        <v>135.4579159827054</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1520708856377095</v>
+        <v>0.1449223889701945</v>
       </c>
       <c r="H35" t="n">
-        <v>64.12747330373745</v>
+        <v>63.22122547725075</v>
       </c>
       <c r="I35" t="n">
-        <v>14.75864912902072</v>
+        <v>14.94592650454215</v>
       </c>
       <c r="J35" t="n">
-        <v>90.44840000000001</v>
+        <v>91.38030000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -1757,22 +1757,22 @@
         <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>141.729672327362</v>
+        <v>138.0993079712946</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1525373414443291</v>
+        <v>0.1477483355707753</v>
       </c>
       <c r="H36" t="n">
-        <v>64.76381800593303</v>
+        <v>63.98364343172564</v>
       </c>
       <c r="I36" t="n">
-        <v>14.18416998452407</v>
+        <v>14.30645092571882</v>
       </c>
       <c r="J36" t="n">
-        <v>90.44840000000001</v>
+        <v>91.38030000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
@@ -1794,22 +1794,22 @@
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>145.1304356352218</v>
+        <v>135.7443160706648</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1561974317087317</v>
+        <v>0.1452287998923414</v>
       </c>
       <c r="H37" t="n">
-        <v>67.1397003536551</v>
+        <v>66.24610509220003</v>
       </c>
       <c r="I37" t="n">
-        <v>16.86072084181234</v>
+        <v>17.09198942962777</v>
       </c>
       <c r="J37" t="n">
-        <v>90.44840000000001</v>
+        <v>91.38030000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
@@ -1831,22 +1831,22 @@
         <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>139.6130799283207</v>
+        <v>135.1678976018377</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1487449630030704</v>
+        <v>0.1487639230630483</v>
       </c>
       <c r="H38" t="n">
-        <v>64.71185346999279</v>
+        <v>63.84822695158873</v>
       </c>
       <c r="I38" t="n">
-        <v>15.69900424719709</v>
+        <v>15.71497969866012</v>
       </c>
       <c r="J38" t="n">
-        <v>88.5228</v>
+        <v>90.12220000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
@@ -1868,22 +1868,22 @@
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>142.7843956342128</v>
+        <v>136.0253106117631</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1521237097335785</v>
+        <v>0.1497075799912453</v>
       </c>
       <c r="H39" t="n">
-        <v>66.53790964519072</v>
+        <v>65.32800222602498</v>
       </c>
       <c r="I39" t="n">
-        <v>16.28621417132149</v>
+        <v>16.43197461207802</v>
       </c>
       <c r="J39" t="n">
-        <v>88.5228</v>
+        <v>90.12220000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -1905,22 +1905,22 @@
         <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>142.7040148311031</v>
+        <v>135.8886327947237</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1520380713421696</v>
+        <v>0.1495571542716831</v>
       </c>
       <c r="H40" t="n">
-        <v>66.76911556347599</v>
+        <v>65.76967556392054</v>
       </c>
       <c r="I40" t="n">
-        <v>16.5545360599002</v>
+        <v>16.71169562889526</v>
       </c>
       <c r="J40" t="n">
-        <v>88.5228</v>
+        <v>90.12220000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -1942,22 +1942,22 @@
         <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>142.9005030467673</v>
+        <v>136.5958053710858</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1522474115586057</v>
+        <v>0.1503354586517077</v>
       </c>
       <c r="H41" t="n">
-        <v>66.24576379522317</v>
+        <v>65.14222633104933</v>
       </c>
       <c r="I41" t="n">
-        <v>15.71432070129602</v>
+        <v>15.87619956885862</v>
       </c>
       <c r="J41" t="n">
-        <v>88.5228</v>
+        <v>90.12220000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
@@ -1979,22 +1979,22 @@
         <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>143.738711927349</v>
+        <v>139.226752714656</v>
       </c>
       <c r="G42" t="n">
-        <v>0.153140446430374</v>
+        <v>0.153231042996407</v>
       </c>
       <c r="H42" t="n">
-        <v>66.32143426171919</v>
+        <v>65.36866511341033</v>
       </c>
       <c r="I42" t="n">
-        <v>14.86384777951283</v>
+        <v>15.04607953504255</v>
       </c>
       <c r="J42" t="n">
-        <v>88.5228</v>
+        <v>90.12220000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
@@ -2016,22 +2016,22 @@
         <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>143.379744775823</v>
+        <v>137.4778367034531</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1527579997735101</v>
+        <v>0.1513062101659023</v>
       </c>
       <c r="H43" t="n">
-        <v>67.85589014284604</v>
+        <v>67.2575980075071</v>
       </c>
       <c r="I43" t="n">
-        <v>17.27929813507093</v>
+        <v>17.40096111790619</v>
       </c>
       <c r="J43" t="n">
-        <v>88.5228</v>
+        <v>90.12220000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44">
@@ -2053,22 +2053,22 @@
         <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>142.1688140692825</v>
+        <v>139.4561357133214</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1524404608874025</v>
+        <v>0.1517729165271969</v>
       </c>
       <c r="H44" t="n">
-        <v>65.90953012036003</v>
+        <v>65.77060313107106</v>
       </c>
       <c r="I44" t="n">
-        <v>16.14524771266841</v>
+        <v>16.17696773669947</v>
       </c>
       <c r="J44" t="n">
-        <v>84.3335</v>
+        <v>85.96980000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
@@ -2090,22 +2090,22 @@
         <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>143.8111983742633</v>
+        <v>142.5023372661519</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1542015068808192</v>
+        <v>0.1550881589268082</v>
       </c>
       <c r="H45" t="n">
-        <v>68.11583824429755</v>
+        <v>67.9420783176751</v>
       </c>
       <c r="I45" t="n">
-        <v>16.99024964025843</v>
+        <v>16.92848186009006</v>
       </c>
       <c r="J45" t="n">
-        <v>84.3335</v>
+        <v>85.96980000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
@@ -2127,22 +2127,22 @@
         <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>143.5269273884763</v>
+        <v>142.2219954625247</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1538966974162825</v>
+        <v>0.1547830573051165</v>
       </c>
       <c r="H46" t="n">
-        <v>68.07765316834001</v>
+        <v>68.11319545815368</v>
       </c>
       <c r="I46" t="n">
-        <v>17.09431247767489</v>
+        <v>17.09469264918624</v>
       </c>
       <c r="J46" t="n">
-        <v>84.3335</v>
+        <v>85.96980000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -2164,22 +2164,22 @@
         <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>143.8130669175647</v>
+        <v>143.3400498088271</v>
       </c>
       <c r="G47" t="n">
-        <v>0.154203510425717</v>
+        <v>0.1559998583308029</v>
       </c>
       <c r="H47" t="n">
-        <v>67.73403496782426</v>
+        <v>67.75575579543283</v>
       </c>
       <c r="I47" t="n">
-        <v>16.60816282999224</v>
+        <v>16.517439778314</v>
       </c>
       <c r="J47" t="n">
-        <v>84.3335</v>
+        <v>85.96980000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
@@ -2201,22 +2201,22 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>145.4657835782098</v>
+        <v>143.7723987483838</v>
       </c>
       <c r="G48" t="n">
-        <v>0.155975635283861</v>
+        <v>0.1564703923749187</v>
       </c>
       <c r="H48" t="n">
-        <v>67.40440828331062</v>
+        <v>67.36596490750692</v>
       </c>
       <c r="I48" t="n">
-        <v>15.60793662916248</v>
+        <v>15.62108072520163</v>
       </c>
       <c r="J48" t="n">
-        <v>84.3335</v>
+        <v>85.96980000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
@@ -2238,22 +2238,22 @@
         <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>146.1951047787457</v>
+        <v>142.0717836932869</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1567576496846456</v>
+        <v>0.1546195788163622</v>
       </c>
       <c r="H49" t="n">
-        <v>68.64081914552145</v>
+        <v>68.59854049608568</v>
       </c>
       <c r="I49" t="n">
-        <v>17.51733680462988</v>
+        <v>17.53948751305687</v>
       </c>
       <c r="J49" t="n">
-        <v>84.3335</v>
+        <v>85.96980000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
@@ -2275,22 +2275,22 @@
         <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>142.5432569556803</v>
+        <v>140.5035365555354</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1521173938101689</v>
+        <v>0.1542579526389805</v>
       </c>
       <c r="H50" t="n">
-        <v>67.33709867442067</v>
+        <v>67.14012904271134</v>
       </c>
       <c r="I50" t="n">
-        <v>17.03554255175757</v>
+        <v>16.77855572426921</v>
       </c>
       <c r="J50" t="n">
-        <v>76.24160000000001</v>
+        <v>80.8069</v>
       </c>
       <c r="K50" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -2312,22 +2312,22 @@
         <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>143.2679284326204</v>
+        <v>143.2387986734098</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1528907389602307</v>
+        <v>0.1572609797839056</v>
       </c>
       <c r="H51" t="n">
-        <v>68.96112978607901</v>
+        <v>69.15017109650091</v>
       </c>
       <c r="I51" t="n">
-        <v>17.71520385942348</v>
+        <v>17.56612145891203</v>
       </c>
       <c r="J51" t="n">
-        <v>76.24160000000001</v>
+        <v>80.8069</v>
       </c>
       <c r="K51" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
@@ -2349,22 +2349,22 @@
         <v>15</v>
       </c>
       <c r="F52" t="n">
-        <v>142.6816826804463</v>
+        <v>143.2878106811118</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1522651171114138</v>
+        <v>0.1573147897601396</v>
       </c>
       <c r="H52" t="n">
-        <v>68.90316598914509</v>
+        <v>69.25342382234466</v>
       </c>
       <c r="I52" t="n">
-        <v>17.7683213640782</v>
+        <v>17.62903108693346</v>
       </c>
       <c r="J52" t="n">
-        <v>76.24160000000001</v>
+        <v>80.8069</v>
       </c>
       <c r="K52" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -2386,22 +2386,22 @@
         <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>143.2549516731119</v>
+        <v>142.9977434678818</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1528768905967325</v>
+        <v>0.1569963267837798</v>
       </c>
       <c r="H53" t="n">
-        <v>68.73101341314954</v>
+        <v>68.79150153040926</v>
       </c>
       <c r="I53" t="n">
-        <v>17.48903001954221</v>
+        <v>17.24195182536418</v>
       </c>
       <c r="J53" t="n">
-        <v>76.24160000000001</v>
+        <v>80.8069</v>
       </c>
       <c r="K53" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
@@ -2423,22 +2423,22 @@
         <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>144.6967103222017</v>
+        <v>143.4110919468037</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1544154871805822</v>
+        <v>0.1574501394894816</v>
       </c>
       <c r="H54" t="n">
-        <v>68.51983258927191</v>
+        <v>68.44816639959558</v>
       </c>
       <c r="I54" t="n">
-        <v>16.7008195747409</v>
+        <v>16.470428619332</v>
       </c>
       <c r="J54" t="n">
-        <v>76.24160000000001</v>
+        <v>80.8069</v>
       </c>
       <c r="K54" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
@@ -2460,22 +2460,22 @@
         <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>145.3546005361375</v>
+        <v>142.5902030405669</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1551175656015085</v>
+        <v>0.1565488907015544</v>
       </c>
       <c r="H55" t="n">
-        <v>69.53866129999898</v>
+        <v>69.47161255037557</v>
       </c>
       <c r="I55" t="n">
-        <v>18.08245708153053</v>
+        <v>17.87587575424212</v>
       </c>
       <c r="J55" t="n">
-        <v>76.24160000000001</v>
+        <v>80.8069</v>
       </c>
       <c r="K55" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
@@ -2497,22 +2497,22 @@
         <v>15</v>
       </c>
       <c r="F56" t="n">
-        <v>144.8058573609884</v>
+        <v>143.703575606618</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1550870808190433</v>
+        <v>0.1568946235188649</v>
       </c>
       <c r="H56" t="n">
-        <v>69.05644261243512</v>
+        <v>69.37129978511456</v>
       </c>
       <c r="I56" t="n">
-        <v>17.51934773533095</v>
+        <v>17.25322366619834</v>
       </c>
       <c r="J56" t="n">
-        <v>66.1887</v>
+        <v>69.1648</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
@@ -2534,22 +2534,22 @@
         <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>146.2673719777658</v>
+        <v>146.7720195963127</v>
       </c>
       <c r="G57" t="n">
-        <v>0.156652363050171</v>
+        <v>0.160244730588363</v>
       </c>
       <c r="H57" t="n">
-        <v>70.42126696661929</v>
+        <v>70.74444499706108</v>
       </c>
       <c r="I57" t="n">
-        <v>18.09375053651591</v>
+        <v>17.85356699894659</v>
       </c>
       <c r="J57" t="n">
-        <v>66.1887</v>
+        <v>69.1648</v>
       </c>
       <c r="K57" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
@@ -2571,22 +2571,22 @@
         <v>15</v>
       </c>
       <c r="F58" t="n">
-        <v>146.5474726390289</v>
+        <v>146.3705410685668</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1569523508730564</v>
+        <v>0.1598063989588562</v>
       </c>
       <c r="H58" t="n">
-        <v>70.48353479650345</v>
+        <v>70.68538944549005</v>
       </c>
       <c r="I58" t="n">
-        <v>18.10750980076299</v>
+        <v>17.87178314907819</v>
       </c>
       <c r="J58" t="n">
-        <v>66.1887</v>
+        <v>69.1648</v>
       </c>
       <c r="K58" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
@@ -2608,22 +2608,22 @@
         <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>146.3188493623991</v>
+        <v>146.1737296123781</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1567074953318098</v>
+        <v>0.1595915214988308</v>
       </c>
       <c r="H59" t="n">
-        <v>70.34229623775231</v>
+        <v>70.5193225611457</v>
       </c>
       <c r="I59" t="n">
-        <v>17.99408597775087</v>
+        <v>17.7287458958243</v>
       </c>
       <c r="J59" t="n">
-        <v>66.1887</v>
+        <v>69.1648</v>
       </c>
       <c r="K59" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
@@ -2645,22 +2645,22 @@
         <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>147.1102125411884</v>
+        <v>146.1370552821332</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1575550453377475</v>
+        <v>0.1595514807050488</v>
       </c>
       <c r="H60" t="n">
-        <v>69.85065729518227</v>
+        <v>70.08702654173052</v>
       </c>
       <c r="I60" t="n">
-        <v>17.37218198802759</v>
+        <v>17.11728956855747</v>
       </c>
       <c r="J60" t="n">
-        <v>66.1887</v>
+        <v>69.1648</v>
       </c>
       <c r="K60" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -2682,22 +2682,22 @@
         <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>146.780930221421</v>
+        <v>146.2093411761242</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1572023839560276</v>
+        <v>0.1596304019711034</v>
       </c>
       <c r="H61" t="n">
-        <v>70.6778196421329</v>
+        <v>70.85402477123932</v>
       </c>
       <c r="I61" t="n">
-        <v>18.24745100208368</v>
+        <v>18.0142953021266</v>
       </c>
       <c r="J61" t="n">
-        <v>66.1887</v>
+        <v>69.1648</v>
       </c>
       <c r="K61" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
@@ -2719,22 +2719,22 @@
         <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>145.6578109533126</v>
+        <v>142.2904946267973</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1523741534061046</v>
+        <v>0.1568219654350349</v>
       </c>
       <c r="H62" t="n">
-        <v>70.41682120992142</v>
+        <v>69.81909524852192</v>
       </c>
       <c r="I62" t="n">
-        <v>17.72235950310882</v>
+        <v>17.59719292025342</v>
       </c>
       <c r="J62" t="n">
-        <v>59.1346</v>
+        <v>57.8445</v>
       </c>
       <c r="K62" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63">
@@ -2756,22 +2756,22 @@
         <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>146.4164590792972</v>
+        <v>144.542397910742</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1531677831137973</v>
+        <v>0.1593038451971655</v>
       </c>
       <c r="H63" t="n">
-        <v>71.45947592493827</v>
+        <v>70.94956129992187</v>
       </c>
       <c r="I63" t="n">
-        <v>18.20185180152373</v>
+        <v>18.15566825614588</v>
       </c>
       <c r="J63" t="n">
-        <v>59.1346</v>
+        <v>57.8445</v>
       </c>
       <c r="K63" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
@@ -2793,22 +2793,22 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>147.491590316845</v>
+        <v>145.4109785097891</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1542924891014103</v>
+        <v>0.1602611299197927</v>
       </c>
       <c r="H64" t="n">
-        <v>71.57586800247053</v>
+        <v>71.10989552525032</v>
       </c>
       <c r="I64" t="n">
-        <v>18.21268999830136</v>
+        <v>18.17584654419774</v>
       </c>
       <c r="J64" t="n">
-        <v>59.1346</v>
+        <v>57.8445</v>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -2830,22 +2830,22 @@
         <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>146.286764976175</v>
+        <v>144.4128368235605</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1530321087614527</v>
+        <v>0.159161052634746</v>
       </c>
       <c r="H65" t="n">
-        <v>71.3810647128962</v>
+        <v>70.84233748466252</v>
       </c>
       <c r="I65" t="n">
-        <v>18.15505759809883</v>
+        <v>18.08725415052123</v>
       </c>
       <c r="J65" t="n">
-        <v>59.1346</v>
+        <v>57.8445</v>
       </c>
       <c r="K65" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66">
@@ -2867,22 +2867,22 @@
         <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>146.6127504256491</v>
+        <v>144.0220557202128</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1533731255360508</v>
+        <v>0.1587303628627933</v>
       </c>
       <c r="H66" t="n">
-        <v>71.09789415288878</v>
+        <v>70.45252450775156</v>
       </c>
       <c r="I66" t="n">
-        <v>17.71423895933281</v>
+        <v>17.67160849612373</v>
       </c>
       <c r="J66" t="n">
-        <v>59.1346</v>
+        <v>57.8445</v>
       </c>
       <c r="K66" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67">
@@ -2904,22 +2904,22 @@
         <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>147.2732861304635</v>
+        <v>146.0582420564878</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1540641188178863</v>
+        <v>0.1609744955020403</v>
       </c>
       <c r="H67" t="n">
-        <v>71.48943493389363</v>
+        <v>71.27314318179464</v>
       </c>
       <c r="I67" t="n">
-        <v>18.26238465073684</v>
+        <v>18.21142924795914</v>
       </c>
       <c r="J67" t="n">
-        <v>59.1346</v>
+        <v>57.8445</v>
       </c>
       <c r="K67" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68">
@@ -2941,22 +2941,22 @@
         <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>148.7597805782322</v>
+        <v>142.2632546679967</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1568928254417948</v>
+        <v>0.1560629931192745</v>
       </c>
       <c r="H68" t="n">
-        <v>71.31403454420922</v>
+        <v>70.35101688578482</v>
       </c>
       <c r="I68" t="n">
-        <v>17.87258261449894</v>
+        <v>18.00976871717543</v>
       </c>
       <c r="J68" t="n">
-        <v>53.4456</v>
+        <v>51.6675</v>
       </c>
       <c r="K68" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69">
@@ -2978,22 +2978,22 @@
         <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>148.5616797290112</v>
+        <v>143.1807825694716</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1566838939561749</v>
+        <v>0.1570695225348202</v>
       </c>
       <c r="H69" t="n">
-        <v>72.07242567019733</v>
+        <v>71.31135587351061</v>
       </c>
       <c r="I69" t="n">
-        <v>18.30613206910235</v>
+        <v>18.48940991277857</v>
       </c>
       <c r="J69" t="n">
-        <v>53.4456</v>
+        <v>51.6675</v>
       </c>
       <c r="K69" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
@@ -3015,22 +3015,22 @@
         <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>148.6373329041255</v>
+        <v>143.2912571864412</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1567636832671781</v>
+        <v>0.1571907133470803</v>
       </c>
       <c r="H70" t="n">
-        <v>72.05171611996778</v>
+        <v>71.36669811275341</v>
       </c>
       <c r="I70" t="n">
-        <v>18.29645250711144</v>
+        <v>18.48818945739852</v>
       </c>
       <c r="J70" t="n">
-        <v>53.4456</v>
+        <v>51.6675</v>
       </c>
       <c r="K70" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71">
@@ -3052,22 +3052,22 @@
         <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>148.7307532048673</v>
+        <v>143.1653766037312</v>
       </c>
       <c r="G71" t="n">
-        <v>0.1568622110740895</v>
+        <v>0.157052622168447</v>
       </c>
       <c r="H71" t="n">
-        <v>72.02512059748021</v>
+        <v>71.31596123812729</v>
       </c>
       <c r="I71" t="n">
-        <v>18.26913907486935</v>
+        <v>18.47866088371262</v>
       </c>
       <c r="J71" t="n">
-        <v>53.4456</v>
+        <v>51.6675</v>
       </c>
       <c r="K71" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72">
@@ -3089,22 +3089,22 @@
         <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>148.7944921193194</v>
+        <v>143.293715853701</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1569294347439559</v>
+        <v>0.1571934105085683</v>
       </c>
       <c r="H72" t="n">
-        <v>71.89966730963306</v>
+        <v>71.0076206741895</v>
       </c>
       <c r="I72" t="n">
-        <v>18.00301463382774</v>
+        <v>18.15588938655483</v>
       </c>
       <c r="J72" t="n">
-        <v>53.4456</v>
+        <v>51.6675</v>
       </c>
       <c r="K72" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
@@ -3126,22 +3126,22 @@
         <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>149.1717736436389</v>
+        <v>143.0687217356795</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1573273431309366</v>
+        <v>0.1569465916404452</v>
       </c>
       <c r="H73" t="n">
-        <v>72.07234087381893</v>
+        <v>71.29456144048636</v>
       </c>
       <c r="I73" t="n">
-        <v>18.33361338506229</v>
+        <v>18.50113833408001</v>
       </c>
       <c r="J73" t="n">
-        <v>53.4456</v>
+        <v>51.6675</v>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
